--- a/results/momentum_failcodes_2026-08-22.xlsx
+++ b/results/momentum_failcodes_2026-08-22.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A480"/>
+  <dimension ref="A1:A539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,21 +559,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CENN</t>
+          <t>ADAMK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BGIN</t>
+          <t>CENN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AEI</t>
+          <t>BGIN</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AEYE</t>
+          <t>AEI</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AIFA</t>
+          <t>AESP</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AIRO</t>
+          <t>AEYE</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AIXC</t>
+          <t>AIFA</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ALOT</t>
+          <t>AIRO</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>AIXC</t>
         </is>
       </c>
     </row>
@@ -755,84 +755,84 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ICG</t>
+          <t>ALOT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CNTY</t>
+          <t>ICG</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMR</t>
+          <t>CNTY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AMPL</t>
+          <t>AMR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INKT</t>
+          <t>ALPX</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EVAX</t>
+          <t>INKT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMTX</t>
+          <t>EVAX</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ANGX</t>
+          <t>AMTX</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KTTA</t>
+          <t>ALRM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FABC</t>
+          <t>KTTA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ANIK</t>
+          <t>FABC</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ANL</t>
+          <t>ANIK</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>APLM</t>
+          <t>AMPL</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>APPF</t>
+          <t>ANGX</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>APPN</t>
+          <t>ANL</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AQST</t>
+          <t>APLM</t>
         </is>
       </c>
     </row>
@@ -958,119 +958,119 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SLDP</t>
+          <t>APPF</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ATLO</t>
+          <t>SLDP</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STEX</t>
+          <t>ATLO</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IMTE</t>
+          <t>APPN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AREC</t>
+          <t>STEX</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TLRY</t>
+          <t>IMTE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KXIN</t>
+          <t>AQST</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>TLRY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AXGN</t>
+          <t>KXIN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ASRV</t>
+          <t>LEE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>AXGN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LNZA</t>
+          <t>VIR</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AXIN</t>
+          <t>LNZA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ATKR</t>
+          <t>AXIN</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OCG</t>
+          <t>AREC</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AYTU</t>
+          <t>OCG</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ATRA</t>
+          <t>AYTU</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ATRC</t>
+          <t>ASRV</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>ATKR</t>
         </is>
       </c>
     </row>
@@ -1133,14 +1133,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AUTL</t>
+          <t>ATRA</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PRHIZ</t>
+          <t>PUSA</t>
         </is>
       </c>
     </row>
@@ -1154,14 +1154,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AVO</t>
+          <t>ATRC</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PUSA</t>
+          <t>SHMD</t>
         </is>
       </c>
     </row>
@@ -1175,42 +1175,42 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AVPT</t>
+          <t>AURA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SHMD</t>
+          <t>BDTX</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BDTX</t>
+          <t>AUTL</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AVR</t>
+          <t>SMSI</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SMSI</t>
+          <t>BEEM</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BEEM</t>
+          <t>AVO</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANL</t>
+          <t>AVPT</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCDA</t>
+          <t>AVR</t>
         </is>
       </c>
     </row>
@@ -1259,2520 +1259,2933 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>BMNP</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BGDE</t>
+          <t>BANL</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BPYPP</t>
+          <t>BCDA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BLKB</t>
+          <t>BEEP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BRNX</t>
+          <t>BPYPP</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BNTC</t>
+          <t>BRNX</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BOLD</t>
+          <t>BGDE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BTBD</t>
+          <t>BLKB</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BPRN</t>
+          <t>BTBD</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>BNTC</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BPYPO</t>
+          <t>BTCS</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BTGO</t>
+          <t>BOLD</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BULLW</t>
+          <t>BTGO</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BPRN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BWB</t>
+          <t>BULLW</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BPYPO</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>BWB</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CDLR</t>
+          <t>BRCB</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BVC</t>
+          <t>CCSI</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BSVN</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BWIN</t>
+          <t>CDLR</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CEPO</t>
+          <t>CDNA</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BYND</t>
+          <t>CEPO</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CHDN</t>
+          <t>BVC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CHTRP</t>
+          <t>BWIN</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CHDN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CING</t>
+          <t>BYND</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CCG</t>
+          <t>CHTRP</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CITR</t>
+          <t>CING</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CELU</t>
+          <t>CITR</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CMMB</t>
+          <t>CCEC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CETY</t>
+          <t>CCG</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMTV</t>
+          <t>CMMB</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CHCI</t>
+          <t>CMTV</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CNOBP</t>
+          <t>CELU</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CHNR</t>
+          <t>CNOBP</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>CETY</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>COCP</t>
+          <t>CNR</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CRBP</t>
+          <t>CHCI</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>COCP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CSHR</t>
+          <t>CHNR</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CRBP</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>CSHR</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>COKE</t>
+          <t>CSTL</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CMPS</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CTRM</t>
+          <t>CNET</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>CTRM</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CPBI</t>
+          <t>COKE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CYCN</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRMD</t>
+          <t>CORT</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CYPH</t>
+          <t>CYCN</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CYPH</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CYRX</t>
+          <t>CPBI</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>CYRX</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CZFS</t>
+          <t>CRMD</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CSAI</t>
+          <t>CZFS</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DCBO</t>
+          <t>CRON</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CSWC</t>
+          <t>DCBO</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>CRVL</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CTKB</t>
+          <t>DCH</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DDI</t>
+          <t>CSAI</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DFDV</t>
+          <t>DDI</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CTW</t>
+          <t>CSWC</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DHCNI</t>
+          <t>DFDV</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CZNC</t>
+          <t>CTKB</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>DHCNI</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DAAQ</t>
+          <t>DMAA</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DMLP</t>
+          <t>CTW</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>DMLP</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DRTS</t>
+          <t>CZNC</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DERM</t>
+          <t>DOX</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>DAAQ</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DSGN</t>
+          <t>DRTS</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DTCX</t>
+          <t>DRUG</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DNUT</t>
+          <t>DSGN</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DTIL</t>
+          <t>DERM</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DUOT</t>
+          <t>DTCX</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DWTX</t>
+          <t>DTIL</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>EDRY</t>
+          <t>DWTX</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ECCU</t>
+          <t>DNUT</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ELBM</t>
+          <t>EDRY</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EFOR</t>
+          <t>DSC</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ELLA</t>
+          <t>ELBM</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EGHA</t>
+          <t>DUOT</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ELMT</t>
+          <t>ELLA</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ELE</t>
+          <t>ELMT</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ENTX</t>
+          <t>ECCU</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ELVN</t>
+          <t>ELOX</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>EFOR</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EROK</t>
+          <t>ENTX</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EGHA</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>EPRX</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EXFY</t>
+          <t>ELE</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EXPO</t>
+          <t>ELVN</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FBLG</t>
+          <t>EXPE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FCBC</t>
+          <t>EROK</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FDMT</t>
+          <t>EXPO</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FHTX</t>
+          <t>ETON</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FBLG</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>FIVE</t>
+          <t>EXFY</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FENC</t>
+          <t>FHTX</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FIZZ</t>
+          <t>FCBC</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>FERA</t>
+          <t>FIVE</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>FLNT</t>
+          <t>FDMT</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>FLYW</t>
+          <t>FIZZ</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FEAM</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FLXS</t>
+          <t>FLNT</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>FTDR</t>
+          <t>FENC</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>FNKO</t>
+          <t>FLYW</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>FTH</t>
+          <t>FERA</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FORR</t>
+          <t>FRHC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>FTDR</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FVN</t>
+          <t>FTH</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>FOXF</t>
+          <t>FLXS</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>FWDI</t>
+          <t>FNKO</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>FVN</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>GAINZ</t>
+          <t>FORR</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>GECCI</t>
+          <t>FWDI</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>FWONA</t>
+          <t>FOX</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>GIBO</t>
+          <t>GAINZ</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>FOXF</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>GECCI</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>GAME</t>
+          <t>FRNM</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>GIBO</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>GCBC</t>
+          <t>GOLD</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>FWONA</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>GDYN</t>
+          <t>GYRE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HELP</t>
+          <t>FWONK</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>GECCG</t>
+          <t>HAIN</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HLXC</t>
+          <t>GAME</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HOLO</t>
+          <t>HELP</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HQI</t>
+          <t>GCBC</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>GLBS</t>
+          <t>HLXC</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HYNE</t>
+          <t>GDYN</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GMRS</t>
+          <t>HOLO</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HYPD</t>
+          <t>GECCG</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>HQI</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>HYNE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>HYPD</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>GLBS</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>GROW</t>
+          <t>GMRS</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>IMPP</t>
+          <t>IDYA</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>GRRR</t>
+          <t>GO</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>GRVY</t>
+          <t>GP</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>INMB</t>
+          <t>IMPP</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>GSHD</t>
+          <t>GRAL</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>GROW</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>GTEC</t>
+          <t>INMB</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>GTIM</t>
+          <t>GRRR</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>INTA</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>GRVY</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>JATT</t>
+          <t>GSHD</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>JUNS</t>
+          <t>IVVD</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GTEC</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>JATT</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HLNE</t>
+          <t>GTIM</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>JUNS</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>HNST</t>
+          <t>GTM</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>LGVN</t>
+          <t>KRT</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>HPK</t>
+          <t>LAUR</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>LOT</t>
+          <t>HCM</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>HQWWW</t>
+          <t>LGVN</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>MANH</t>
+          <t>HLNE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>HRZN</t>
+          <t>LOT</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MCRI</t>
+          <t>HNST</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MEDP</t>
+          <t>MANH</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>HUDI</t>
+          <t>HPK</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>MCAH</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>HURC</t>
+          <t>HQWWW</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MFIN</t>
+          <t>MCRI</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>IACO</t>
+          <t>HRZN</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IMCR</t>
+          <t>MEDP</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MRDN</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>HUDI</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>IMUX</t>
+          <t>MFIN</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MSBIP</t>
+          <t>HURC</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>IACO</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>NAKA</t>
+          <t>MRDN</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>INDI</t>
+          <t>IMC</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>NBP</t>
+          <t>IMCR</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>INO</t>
+          <t>MSBIP</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>NCI</t>
+          <t>IMMX</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>IPHA</t>
+          <t>NAKA</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>JAN</t>
+          <t>IMUX</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>NMFCZ</t>
+          <t>NBP</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>JFU</t>
+          <t>INBX</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>NRC</t>
+          <t>NCI</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>INDI</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>INO</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>NTRB</t>
+          <t>NMFCZ</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>KELYA</t>
+          <t>IPHA</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>KLTR</t>
+          <t>NRC</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>NVCT</t>
+          <t>JAN</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>KMDA</t>
+          <t>JFU</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ODTX</t>
+          <t>NTRB</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>KOPN</t>
+          <t>JKHY</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OMEX</t>
+          <t>JOYY</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>KPRX</t>
+          <t>NVCT</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ONBPO</t>
+          <t>KELYA</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>KRKR</t>
+          <t>OCAC</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ORBS</t>
+          <t>KLTR</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>KRNY</t>
+          <t>ODTX</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>OTLY</t>
+          <t>KMDA</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>KSPI</t>
+          <t>OMEX</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>OVLY</t>
+          <t>KOPN</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>KWY</t>
+          <t>ONBPO</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>KZIA</t>
+          <t>KPRX</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ORBS</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>PANL</t>
+          <t>KRKR</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>LEGH</t>
+          <t>OTLY</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>PAYS</t>
+          <t>KRNY</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>LEXX</t>
+          <t>OVLY</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>PEBK</t>
+          <t>KSPI</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>KWY</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>LMRI</t>
+          <t>KZIA</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>PFX</t>
+          <t>PANL</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>LPTH</t>
+          <t>LECO</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>LSE</t>
+          <t>PAYS</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>PRGS</t>
+          <t>LEGH</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>PRZO</t>
+          <t>PBLS</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MAKO</t>
+          <t>LEXX</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>PSEC</t>
+          <t>PEBK</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>MASS</t>
+          <t>LIFE</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>MBINL</t>
+          <t>LMRI</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PFX</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>MCFT</t>
+          <t>LPTH</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>PXS</t>
+          <t>PHOS</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>LSE</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>PYPD</t>
+          <t>LTGO</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>MGTX</t>
+          <t>PRGS</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>RDI</t>
+          <t>PRZO</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>MGYR</t>
+          <t>MAKO</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>PSEC</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>MICC</t>
+          <t>MASS</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>REFI</t>
+          <t>MBINL</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>PTLO</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>RENT</t>
+          <t>MCFT</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MLAB</t>
+          <t>PXS</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>MMED</t>
+          <t>MELI</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>PYPD</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>MNKD</t>
+          <t>MGTX</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>RMBI</t>
+          <t>RDI</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>MNOV</t>
+          <t>MGYR</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>RMNI</t>
+          <t>REAX</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>MOLN</t>
+          <t>MICC</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>RMR</t>
+          <t>REFI</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>MRX</t>
+          <t>MINE</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>RNAC</t>
+          <t>RENT</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MTEX</t>
+          <t>MLAB</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MYSE</t>
+          <t>MMED</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>MYSZ</t>
+          <t>RGLD</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>MNKD</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>NAVI</t>
+          <t>RMBI</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MNOV</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>NICM</t>
+          <t>RMNI</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SBMT</t>
+          <t>MOLN</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>NIPG</t>
+          <t>RMR</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>MRX</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>NIQ</t>
+          <t>RNAC</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>SHIP</t>
+          <t>MTEX</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>NPAC</t>
+          <t>MYSE</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>SIBN</t>
+          <t>MYSZ</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>NSIT</t>
+          <t>SATA</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>SLDE</t>
+          <t>NAVI</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>NTHI</t>
+          <t>NEO</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>SMJF</t>
+          <t>NICM</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>SBMT</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>NIPG</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>NXPL</t>
+          <t>SEIC</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>SRTA</t>
+          <t>NIQ</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>OABI</t>
+          <t>SHIP</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>OBIO</t>
+          <t>NPAC</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>OCCI</t>
+          <t>SIBN</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>STRD</t>
+          <t>NSIT</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>OESX</t>
+          <t>SIND</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>NTHI</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>OGC</t>
+          <t>SLDE</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>NWS</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>OGG</t>
+          <t>SMJF</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>SYRE</t>
+          <t>SMTI</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>OGI</t>
+          <t>NXPL</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>OABI</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TBPH</t>
+          <t>SRTA</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>OMSE</t>
+          <t>OBIO</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TCBX</t>
+          <t>SSMR</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>OXLCG</t>
+          <t>OCCI</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>OESX</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>TII</t>
+          <t>OGC</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>TOP</t>
+          <t>STRD</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>PBAM</t>
+          <t>OGG</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TRLV</t>
+          <t>STRF</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>PBM</t>
+          <t>OGI</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>STRK</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>PCTY</t>
+          <t>SYRE</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>OMSE</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>TAYD</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>PHOE</t>
+          <t>OXLCG</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>TWAV</t>
+          <t>TBPH</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>PLSE</t>
+          <t>OXLCM</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>VGNT</t>
+          <t>TCBX</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>PMN</t>
+          <t>PBAM</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>VMET</t>
+          <t>TII</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>PMTS</t>
+          <t>PBM</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>VOXR</t>
+          <t>TOP</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>PMTW</t>
+          <t>PCTY</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>XXI</t>
+          <t>TRLV</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>PEPG</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>PRAA</t>
+          <t>TRMD</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>PHOE</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>PRHI</t>
+          <t>TRON</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PRLD</t>
+          <t>PLSE</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>PROV</t>
+          <t>PLUN</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>PRPO</t>
+          <t>TWAV</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>PRQR</t>
+          <t>PMN</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PRTA</t>
+          <t>USDE</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>PRTS</t>
+          <t>PMTS</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>PSUS</t>
+          <t>USDEW</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>PMTW</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>QMCO</t>
+          <t>VGNT</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>QTTB</t>
+          <t>PMVP</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>RBKB</t>
+          <t>VMET</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>RCBC</t>
+          <t>VOGX</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>RCEL</t>
+          <t>PRAA</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>RDVT</t>
+          <t>VOXR</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>RILYG</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>RMCO</t>
+          <t>WHK</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>RMTI</t>
+          <t>PRHI</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>XXI</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>RRGB</t>
+          <t>PRLD</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>RUM</t>
+          <t>PROV</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>RWAYI</t>
+          <t>PRPO</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>SAFT</t>
+          <t>PRQR</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>PRTA</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>SATL</t>
+          <t>PRTS</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>PSUS</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>PTC</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>SCYX</t>
+          <t>QMCO</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>SENEA</t>
+          <t>QTTB</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>SLNG</t>
+          <t>RBKB</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>RCBC</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>RCEL</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>SPAI</t>
+          <t>RDVT</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>SPCB</t>
+          <t>RILYG</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>SPEG</t>
+          <t>RMCO</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>SPSC</t>
+          <t>RMTI</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>ROP</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>STEP</t>
+          <t>RRGB</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>STRA</t>
+          <t>RUM</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SUNC</t>
+          <t>RWAYI</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>TECX</t>
+          <t>SAFT</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SAIH</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>TILE</t>
+          <t>SATL</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>TKNO</t>
+          <t>SAV</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>TLF</t>
+          <t>SBC</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SCTX</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>SCYX</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>SENEA</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>VACI</t>
+          <t>SLNG</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>XNCR</t>
+          <t>SLP</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
+          <t>SMCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>SPAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>SPCB</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>SPEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>SPSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>SQFTP</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>SUNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>TECX</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>TILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>TKNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>TLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>TMDX</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>TRIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>VACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
           <t>XRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>FCUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>DAAQU</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ABOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>CABA</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>IXHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ANIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>KGEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>GCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>CGEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>BFRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>GWRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>RIGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>ACHV</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>CHRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>ISNRW</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>YDES</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>ACRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>IPST</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CSTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>LNSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>BIXIW</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>NBTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>BRR</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>RDZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>CHRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>ORMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>ACON</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>HWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>ALEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>GNLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>RCMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>AEHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>FORTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>KBSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>NERV</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>CLYM</t>
         </is>
       </c>
     </row>
